--- a/customer_data.xlsx
+++ b/customer_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suraj\jup-note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC7E259-9E61-4E82-BAFD-446A9E1932F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E8D1F4-472F-4377-9EF5-D2E584ABD9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$D$1:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$I$1:$I$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="184">
   <si>
     <t>CustomerID</t>
   </si>
@@ -586,9 +586,6 @@
   </si>
   <si>
     <t>Customer_Lifespan_Months</t>
-  </si>
-  <si>
-    <t>XXXX</t>
   </si>
 </sst>
 </file>
@@ -661,7 +658,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3922,8 +3919,8 @@
       <c r="H78">
         <v>63.082000000000001</v>
       </c>
-      <c r="I78" t="s">
-        <v>184</v>
+      <c r="I78">
+        <v>2</v>
       </c>
       <c r="J78" t="s">
         <v>33</v>
@@ -4088,6 +4085,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="I1:I82" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text=" ">
       <formula>NOT(ISERROR(SEARCH(" ",D1)))</formula>
